--- a/OUTPUT/direct_Q9L4P1_Staphylococcus_aureus_subsp__aureus_COL.xlsx
+++ b/OUTPUT/direct_Q9L4P1_Staphylococcus_aureus_subsp__aureus_COL.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9822071171531388</v>
       </c>
     </row>
   </sheetData>
